--- a/data/documents/bill-of-quantities.xlsx
+++ b/data/documents/bill-of-quantities.xlsx
@@ -316,13 +316,13 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <v>21.06</v>
+        <v>72.9</v>
       </c>
       <c r="F3" s="3">
         <v>575.0</v>
       </c>
       <c r="G3" s="3">
-        <v>12109.5</v>
+        <v>41917.5</v>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
@@ -398,13 +398,13 @@
         </is>
       </c>
       <c r="E5" s="2">
-        <v>4.9702</v>
+        <v>17.2044</v>
       </c>
       <c r="F5" s="3">
         <v>42.0</v>
       </c>
       <c r="G5" s="3">
-        <v>208.75</v>
+        <v>722.58</v>
       </c>
       <c r="H5" s="0" t="inlineStr">
         <is>
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="E8" s="2">
-        <v>1.1232</v>
+        <v>3.888</v>
       </c>
       <c r="F8" s="3">
         <v>950.0</v>
       </c>
       <c r="G8" s="3">
-        <v>1067.04</v>
+        <v>3693.6</v>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
@@ -603,13 +603,13 @@
         </is>
       </c>
       <c r="E10" s="2">
-        <v>0.351</v>
+        <v>1.215</v>
       </c>
       <c r="F10" s="3">
         <v>3500.0</v>
       </c>
       <c r="G10" s="3">
-        <v>1228.5</v>
+        <v>4252.5</v>
       </c>
       <c r="H10" s="0" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="E11" s="3">
-        <v>5.76</v>
+        <v>28.8</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <v>14613.79</v>
+        <v>50586.18</v>
       </c>
     </row>
     <row r="4">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <v>2071.67</v>
+        <v>4698.23</v>
       </c>
     </row>
     <row r="3">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <v>69803.3</v>
+        <v>72827.3</v>
       </c>
     </row>
     <row r="4">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <v>48746.94</v>
+        <v>79068.77</v>
       </c>
     </row>
   </sheetData>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <v>120621.91</v>
+        <v>156594.3</v>
       </c>
     </row>
     <row r="3">
